--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_antofagasta.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_antofagasta.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>28.59076411256311</v>
+      </c>
+      <c r="C2">
         <v>20.49729890897108</v>
-      </c>
-      <c r="C2">
-        <v>28.59076411256311</v>
       </c>
       <c r="D2">
         <v>4.878691599517675</v>
       </c>
       <c r="E2">
-        <v>13.74845074351154</v>
+        <v>19.17709810773615</v>
       </c>
       <c r="F2">
         <v>67.0744511487523</v>
       </c>
       <c r="G2">
-        <v>19.17709810773615</v>
+        <v>13.74845074351154</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>30.99658557405036</v>
+      </c>
+      <c r="C3">
         <v>18.1284677763551</v>
-      </c>
-      <c r="C3">
-        <v>30.99658557405036</v>
       </c>
       <c r="D3">
         <v>5.516185991759858</v>
       </c>
       <c r="E3">
-        <v>12.1565540927304</v>
+        <v>20.78563251287922</v>
       </c>
       <c r="F3">
         <v>67.05781339439038</v>
       </c>
       <c r="G3">
-        <v>20.78563251287922</v>
+        <v>12.1565540927304</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>39.47078280044101</v>
+      </c>
+      <c r="C4">
         <v>13.56119073869901</v>
-      </c>
-      <c r="C4">
-        <v>39.47078280044101</v>
       </c>
       <c r="D4">
         <v>7.373983739837398</v>
       </c>
       <c r="E4">
-        <v>8.861671469740633</v>
+        <v>25.79250720461095</v>
       </c>
       <c r="F4">
-        <v>65.3458213256484</v>
+        <v>65.34582132564842</v>
       </c>
       <c r="G4">
-        <v>25.79250720461095</v>
+        <v>8.861671469740635</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>31.64239075841286</v>
+      </c>
+      <c r="C5">
         <v>27.23505775991964</v>
-      </c>
-      <c r="C5">
-        <v>31.64239075841286</v>
       </c>
       <c r="D5">
         <v>3.671738128169663</v>
       </c>
       <c r="E5">
-        <v>17.14217972022445</v>
+        <v>19.91622540109065</v>
       </c>
       <c r="F5">
         <v>62.9415948786849</v>
       </c>
       <c r="G5">
-        <v>19.91622540109065</v>
+        <v>17.14217972022445</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>30.72599411402368</v>
+      </c>
+      <c r="C6">
         <v>17.69984942851276</v>
-      </c>
-      <c r="C6">
-        <v>30.72599411402368</v>
       </c>
       <c r="D6">
         <v>5.649765575909904</v>
       </c>
       <c r="E6">
+        <v>20.70124270859752</v>
+      </c>
+      <c r="F6">
+        <v>67.37371175616168</v>
+      </c>
+      <c r="G6">
         <v>11.92504553524082</v>
-      </c>
-      <c r="F6">
-        <v>67.37371175616167</v>
-      </c>
-      <c r="G6">
-        <v>20.70124270859752</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>36.92307692307693</v>
+      </c>
+      <c r="C7">
         <v>19.23076923076923</v>
-      </c>
-      <c r="C7">
-        <v>36.92307692307693</v>
       </c>
       <c r="D7">
         <v>5.2</v>
       </c>
       <c r="E7">
-        <v>12.31527093596059</v>
+        <v>23.64532019704434</v>
       </c>
       <c r="F7">
         <v>64.03940886699507</v>
       </c>
       <c r="G7">
-        <v>23.64532019704434</v>
+        <v>12.31527093596059</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>33.57202331390508</v>
+      </c>
+      <c r="C8">
         <v>14.90424646128226</v>
-      </c>
-      <c r="C8">
-        <v>33.57202331390508</v>
       </c>
       <c r="D8">
         <v>6.709497206703911</v>
       </c>
       <c r="E8">
-        <v>10.03813369223867</v>
+        <v>22.61103633916554</v>
       </c>
       <c r="F8">
         <v>67.35082996859578</v>
       </c>
       <c r="G8">
-        <v>22.61103633916554</v>
+        <v>10.03813369223867</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>32.77449247088947</v>
+      </c>
+      <c r="C9">
         <v>27.94001097360239</v>
-      </c>
-      <c r="C9">
-        <v>32.77449247088947</v>
       </c>
       <c r="D9">
         <v>3.579096661575387</v>
       </c>
       <c r="E9">
-        <v>17.38487216447917</v>
+        <v>20.39298990971853</v>
       </c>
       <c r="F9">
         <v>62.22213792580229</v>
       </c>
       <c r="G9">
-        <v>20.39298990971853</v>
+        <v>17.38487216447917</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>29.50179094757408</v>
+      </c>
+      <c r="C10">
         <v>20.05861282969717</v>
-      </c>
-      <c r="C10">
-        <v>29.50179094757408</v>
       </c>
       <c r="D10">
         <v>4.98538961038961</v>
       </c>
       <c r="E10">
-        <v>13.41171347703026</v>
+        <v>19.72566949706075</v>
       </c>
       <c r="F10">
         <v>66.862617025909</v>
       </c>
       <c r="G10">
-        <v>19.72566949706075</v>
+        <v>13.41171347703026</v>
       </c>
     </row>
   </sheetData>
